--- a/scoring/2027/results/ASICS_2027_Scores.xlsx
+++ b/scoring/2027/results/ASICS_2027_Scores.xlsx
@@ -35,17 +35,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF6D5"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -65,12 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -474,15 +468,17 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0.9</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
       <c r="C2">
         <f>IFERROR(ROUND(AVERAGE(B2),2),"")</f>
         <v/>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -491,7 +487,7 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>?</t>
         </is>
@@ -501,11 +497,11 @@
         <v/>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>ASICS score = the average of the city's vertical scores (equal weights). Yellow = provisional: some main questions aren't scored yet. NA = no question applies.</t>
         </is>
@@ -594,11 +590,7 @@
           <t>UPD1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -608,9 +600,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6.25</v>
       </c>
     </row>
     <row r="3">
@@ -624,11 +613,7 @@
           <t>UPD1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -637,11 +622,6 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -656,11 +636,7 @@
           <t>UPD1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -669,11 +645,6 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -688,11 +659,7 @@
           <t>UPD1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -701,11 +668,6 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -720,11 +682,7 @@
           <t>UPD1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -733,11 +691,6 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -752,11 +705,7 @@
           <t>UPD1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -765,11 +714,6 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -784,11 +728,7 @@
           <t>UPD1</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -797,11 +737,6 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -816,11 +751,7 @@
           <t>UPD1a</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -830,9 +761,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="10">
@@ -846,11 +774,7 @@
           <t>UPD1a</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -859,11 +783,6 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -878,11 +797,7 @@
           <t>UPD1a</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -892,9 +807,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G11" t="n">
-        <v>3.75</v>
       </c>
     </row>
     <row r="12">
@@ -908,11 +820,7 @@
           <t>UPD1a</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -922,9 +830,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -938,11 +843,7 @@
           <t>UPD1a</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -952,9 +853,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -968,11 +866,7 @@
           <t>UPD1a</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -981,11 +875,6 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1000,11 +889,7 @@
           <t>UPD1a</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -1013,11 +898,6 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1032,11 +912,7 @@
           <t>UPD1b</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -1046,9 +922,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G16" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1062,11 +935,7 @@
           <t>UPD1b</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -1075,11 +944,6 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1094,11 +958,7 @@
           <t>UPD1b</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -1107,11 +967,6 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1126,11 +981,7 @@
           <t>UPD1b</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -1139,11 +990,6 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1158,11 +1004,7 @@
           <t>UPD1b</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -1171,11 +1013,6 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1190,11 +1027,7 @@
           <t>UPD1b</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -1203,11 +1036,6 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1222,11 +1050,7 @@
           <t>UPD1b</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -1235,11 +1059,6 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1254,11 +1073,7 @@
           <t>UPD2</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -1267,11 +1082,6 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1286,11 +1096,7 @@
           <t>UPD2</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -1299,11 +1105,6 @@
       <c r="E24" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1318,11 +1119,7 @@
           <t>UPD2</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -1331,11 +1128,6 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1350,11 +1142,7 @@
           <t>UPD2</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -1363,11 +1151,6 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1382,11 +1165,7 @@
           <t>UPD2</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -1395,11 +1174,6 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1414,11 +1188,7 @@
           <t>UPD2</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -1427,11 +1197,6 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1446,11 +1211,7 @@
           <t>UPD2</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -1459,11 +1220,6 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1478,11 +1234,7 @@
           <t>UPD2a</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -1492,9 +1244,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1508,11 +1257,7 @@
           <t>UPD2a</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -1521,11 +1266,6 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1540,11 +1280,7 @@
           <t>UPD2a</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -1553,11 +1289,6 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1572,11 +1303,7 @@
           <t>UPD2a</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -1585,11 +1312,6 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1604,11 +1326,7 @@
           <t>UPD2a</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -1617,11 +1335,6 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1636,11 +1349,7 @@
           <t>UPD2a</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -1649,11 +1358,6 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1668,11 +1372,7 @@
           <t>UPD2a</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -1681,11 +1381,6 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1700,11 +1395,7 @@
           <t>UPD2b</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -1713,11 +1404,6 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -1732,11 +1418,7 @@
           <t>UPD2b</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -1745,11 +1427,6 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1764,11 +1441,7 @@
           <t>UPD2b</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -1777,11 +1450,6 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1796,11 +1464,7 @@
           <t>UPD2b</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -1809,11 +1473,6 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1828,11 +1487,7 @@
           <t>UPD2b</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -1841,11 +1496,6 @@
       <c r="E41" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1860,11 +1510,7 @@
           <t>UPD2b</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -1873,11 +1519,6 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1892,11 +1533,7 @@
           <t>UPD2b</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -1905,11 +1542,6 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1924,11 +1556,7 @@
           <t>UPD2c</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -1937,11 +1565,6 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -1956,11 +1579,7 @@
           <t>UPD2c</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -1970,9 +1589,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G45" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="46">
@@ -1986,11 +1602,7 @@
           <t>UPD2c</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -1999,11 +1611,6 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2018,11 +1625,7 @@
           <t>UPD2c</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -2031,11 +1634,6 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2050,11 +1648,7 @@
           <t>UPD2c</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -2063,11 +1657,6 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2082,11 +1671,7 @@
           <t>UPD2c</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -2095,11 +1680,6 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2114,11 +1694,7 @@
           <t>UPD2c</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -2127,11 +1703,6 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2146,11 +1717,7 @@
           <t>UPD2d</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -2159,11 +1726,6 @@
       <c r="E51" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2178,11 +1740,7 @@
           <t>UPD2d</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -2191,11 +1749,6 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -2210,11 +1763,7 @@
           <t>UPD2d</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -2223,11 +1772,6 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2242,11 +1786,7 @@
           <t>UPD2d</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -2255,11 +1795,6 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2274,11 +1809,7 @@
           <t>UPD2d</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -2287,11 +1818,6 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2306,11 +1832,7 @@
           <t>UPD2d</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -2319,11 +1841,6 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2338,11 +1855,7 @@
           <t>UPD2d</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -2351,11 +1864,6 @@
       <c r="E57" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2370,11 +1878,7 @@
           <t>UPD3</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -2384,9 +1888,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G58" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -2400,11 +1901,7 @@
           <t>UPD3</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -2413,11 +1910,6 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2432,11 +1924,7 @@
           <t>UPD3</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -2445,11 +1933,6 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2464,11 +1947,7 @@
           <t>UPD3</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -2477,11 +1956,6 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2496,11 +1970,7 @@
           <t>UPD3</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -2509,11 +1979,6 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2528,11 +1993,7 @@
           <t>UPD3</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -2541,11 +2002,6 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2560,11 +2016,7 @@
           <t>UPD3</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -2573,11 +2025,6 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2592,11 +2039,7 @@
           <t>UPD3a</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -2606,9 +2049,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G65" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="66">
@@ -2622,11 +2062,7 @@
           <t>UPD3a</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -2635,11 +2071,6 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2654,11 +2085,7 @@
           <t>UPD3a</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -2667,11 +2094,6 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2686,11 +2108,7 @@
           <t>UPD3a</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -2699,11 +2117,6 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2718,11 +2131,7 @@
           <t>UPD3a</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -2731,11 +2140,6 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2750,11 +2154,7 @@
           <t>UPD3a</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -2763,11 +2163,6 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2782,11 +2177,7 @@
           <t>UPD3a</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -2795,11 +2186,6 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2814,11 +2200,7 @@
           <t>UPD3b</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -2828,9 +2210,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G72" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="73">
@@ -2844,11 +2223,7 @@
           <t>UPD3b</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -2857,11 +2232,6 @@
       <c r="E73" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2876,11 +2246,7 @@
           <t>UPD3b</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -2889,11 +2255,6 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2908,11 +2269,7 @@
           <t>UPD3b</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -2921,11 +2278,6 @@
       <c r="E75" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2940,11 +2292,7 @@
           <t>UPD3b</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -2953,11 +2301,6 @@
       <c r="E76" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -2972,11 +2315,7 @@
           <t>UPD3b</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -2985,11 +2324,6 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3004,11 +2338,7 @@
           <t>UPD3b</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -3017,11 +2347,6 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3036,11 +2361,7 @@
           <t>UPD4</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -3049,11 +2370,6 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3068,11 +2384,7 @@
           <t>UPD4</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -3081,11 +2393,6 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -3100,11 +2407,7 @@
           <t>UPD4</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -3113,11 +2416,6 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3132,11 +2430,7 @@
           <t>UPD4</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -3145,11 +2439,6 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3164,11 +2453,7 @@
           <t>UPD4</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -3177,11 +2462,6 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3196,11 +2476,7 @@
           <t>UPD4</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -3209,11 +2485,6 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3228,11 +2499,7 @@
           <t>UPD4</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -3241,11 +2508,6 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3260,11 +2522,7 @@
           <t>UPD4a</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -3273,11 +2531,6 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3292,11 +2545,7 @@
           <t>UPD4a</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -3305,11 +2554,6 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -3324,11 +2568,7 @@
           <t>UPD4a</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -3337,11 +2577,6 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3356,11 +2591,7 @@
           <t>UPD4a</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -3369,11 +2600,6 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3388,11 +2614,7 @@
           <t>UPD4a</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -3401,11 +2623,6 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3420,11 +2637,7 @@
           <t>UPD4a</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -3433,11 +2646,6 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3452,11 +2660,7 @@
           <t>UPD4a</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -3465,11 +2669,6 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3484,11 +2683,7 @@
           <t>UPD4b</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -3497,11 +2692,6 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3516,11 +2706,7 @@
           <t>UPD4b</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -3530,9 +2716,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G94" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="95">
@@ -3546,11 +2729,7 @@
           <t>UPD4b</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -3559,11 +2738,6 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3578,11 +2752,7 @@
           <t>UPD4b</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -3591,11 +2761,6 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3610,11 +2775,7 @@
           <t>UPD4b</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -3623,11 +2784,6 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3642,11 +2798,7 @@
           <t>UPD4b</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -3655,11 +2807,6 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3674,11 +2821,7 @@
           <t>UPD4b</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -3687,11 +2830,6 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3706,11 +2844,7 @@
           <t>UPD5</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -3720,9 +2854,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G100" t="n">
-        <v>7.5</v>
       </c>
     </row>
     <row r="101">
@@ -3736,11 +2867,7 @@
           <t>UPD5</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -3749,11 +2876,6 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3768,11 +2890,7 @@
           <t>UPD5</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -3781,11 +2899,6 @@
       <c r="E102" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3800,11 +2913,7 @@
           <t>UPD5</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -3813,11 +2922,6 @@
       <c r="E103" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3832,11 +2936,7 @@
           <t>UPD5</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -3845,11 +2945,6 @@
       <c r="E104" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3864,11 +2959,7 @@
           <t>UPD5</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -3877,11 +2968,6 @@
       <c r="E105" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3896,11 +2982,7 @@
           <t>UPD5</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -3909,11 +2991,6 @@
       <c r="E106" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3928,11 +3005,7 @@
           <t>UPD5a</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -3942,9 +3015,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G107" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="108">
@@ -3958,11 +3028,7 @@
           <t>UPD5a</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -3971,11 +3037,6 @@
       <c r="E108" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -3990,11 +3051,7 @@
           <t>UPD5a</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -4003,11 +3060,6 @@
       <c r="E109" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4022,11 +3074,7 @@
           <t>UPD5a</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -4035,11 +3083,6 @@
       <c r="E110" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4054,11 +3097,7 @@
           <t>UPD5a</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -4067,11 +3106,6 @@
       <c r="E111" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4086,11 +3120,7 @@
           <t>UPD5a</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -4099,11 +3129,6 @@
       <c r="E112" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4118,11 +3143,7 @@
           <t>UPD5a</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -4131,11 +3152,6 @@
       <c r="E113" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4150,11 +3166,7 @@
           <t>UPD5b</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -4164,9 +3176,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G114" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -4180,11 +3189,7 @@
           <t>UPD5b</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -4193,11 +3198,6 @@
       <c r="E115" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4212,11 +3212,7 @@
           <t>UPD5b</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -4225,11 +3221,6 @@
       <c r="E116" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4244,11 +3235,7 @@
           <t>UPD5b</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -4257,11 +3244,6 @@
       <c r="E117" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4276,11 +3258,7 @@
           <t>UPD5b</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -4289,11 +3267,6 @@
       <c r="E118" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4308,11 +3281,7 @@
           <t>UPD5b</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -4321,11 +3290,6 @@
       <c r="E119" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4340,11 +3304,7 @@
           <t>UPD5b</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -4353,11 +3313,6 @@
       <c r="E120" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4372,11 +3327,7 @@
           <t>UPD6</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -4385,11 +3336,6 @@
       <c r="E121" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4404,11 +3350,7 @@
           <t>UPD6</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -4418,9 +3360,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G122" t="n">
-        <v>3.75</v>
       </c>
     </row>
     <row r="123">
@@ -4434,11 +3373,7 @@
           <t>UPD6</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -4447,11 +3382,6 @@
       <c r="E123" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4466,11 +3396,7 @@
           <t>UPD6</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -4479,11 +3405,6 @@
       <c r="E124" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4498,11 +3419,7 @@
           <t>UPD6</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -4511,11 +3428,6 @@
       <c r="E125" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4530,11 +3442,7 @@
           <t>UPD6</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -4543,11 +3451,6 @@
       <c r="E126" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4562,11 +3465,7 @@
           <t>UPD6</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -4575,11 +3474,6 @@
       <c r="E127" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4594,11 +3488,7 @@
           <t>UPD6a</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -4607,11 +3497,6 @@
       <c r="E128" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4626,11 +3511,7 @@
           <t>UPD6a</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -4640,9 +3521,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G129" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="130">
@@ -4656,11 +3534,7 @@
           <t>UPD6a</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -4669,11 +3543,6 @@
       <c r="E130" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4688,11 +3557,7 @@
           <t>UPD6a</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -4701,11 +3566,6 @@
       <c r="E131" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4720,11 +3580,7 @@
           <t>UPD6a</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -4733,11 +3589,6 @@
       <c r="E132" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4752,11 +3603,7 @@
           <t>UPD6a</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -4765,11 +3612,6 @@
       <c r="E133" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4784,11 +3626,7 @@
           <t>UPD6a</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -4797,11 +3635,6 @@
       <c r="E134" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4816,11 +3649,7 @@
           <t>UPD6b</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -4829,11 +3658,6 @@
       <c r="E135" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4848,11 +3672,7 @@
           <t>UPD6b</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -4862,9 +3682,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G136" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="137">
@@ -4878,11 +3695,7 @@
           <t>UPD6b</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -4891,11 +3704,6 @@
       <c r="E137" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4910,11 +3718,7 @@
           <t>UPD6b</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -4923,11 +3727,6 @@
       <c r="E138" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4942,11 +3741,7 @@
           <t>UPD6b</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -4955,11 +3750,6 @@
       <c r="E139" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -4974,11 +3764,7 @@
           <t>UPD6b</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -4987,11 +3773,6 @@
       <c r="E140" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5006,11 +3787,7 @@
           <t>UPD6b</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -5019,11 +3796,6 @@
       <c r="E141" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -5038,11 +3810,7 @@
           <t>DPG1</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -5052,9 +3820,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G142" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="143">
@@ -5068,11 +3833,7 @@
           <t>DPG1</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -5081,11 +3842,6 @@
       <c r="E143" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5100,11 +3856,7 @@
           <t>DPG1</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -5114,9 +3866,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G144" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="145">
@@ -5130,11 +3879,7 @@
           <t>DPG1</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -5144,9 +3889,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G145" t="n">
-        <v>7.5</v>
       </c>
     </row>
     <row r="146">
@@ -5160,11 +3902,7 @@
           <t>DPG1</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -5173,11 +3911,6 @@
       <c r="E146" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5192,11 +3925,7 @@
           <t>DPG1</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -5205,11 +3934,6 @@
       <c r="E147" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5224,11 +3948,7 @@
           <t>DPG1</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -5237,11 +3957,6 @@
       <c r="E148" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5256,11 +3971,7 @@
           <t>DPG1a</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -5270,9 +3981,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G149" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -5286,11 +3994,7 @@
           <t>DPG1a</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -5299,11 +4003,6 @@
       <c r="E150" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5318,11 +4017,7 @@
           <t>DPG1a</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -5332,9 +4027,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G151" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -5348,11 +4040,7 @@
           <t>DPG1a</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -5362,9 +4050,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G152" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -5378,11 +4063,7 @@
           <t>DPG1a</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -5391,11 +4072,6 @@
       <c r="E153" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5410,11 +4086,7 @@
           <t>DPG1a</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -5423,11 +4095,6 @@
       <c r="E154" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5442,11 +4109,7 @@
           <t>DPG1a</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -5455,11 +4118,6 @@
       <c r="E155" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5474,11 +4132,7 @@
           <t>DPG1b</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -5488,9 +4142,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G156" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="157">
@@ -5504,11 +4155,7 @@
           <t>DPG1b</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -5517,11 +4164,6 @@
       <c r="E157" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5536,11 +4178,7 @@
           <t>DPG1b</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -5550,9 +4188,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G158" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="159">
@@ -5566,11 +4201,7 @@
           <t>DPG1b</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -5580,9 +4211,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G159" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="160">
@@ -5596,11 +4224,7 @@
           <t>DPG1b</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -5610,9 +4234,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G160" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="161">
@@ -5626,11 +4247,7 @@
           <t>DPG1b</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -5639,11 +4256,6 @@
       <c r="E161" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5658,11 +4270,7 @@
           <t>DPG1b</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -5671,11 +4279,6 @@
       <c r="E162" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5690,11 +4293,7 @@
           <t>DPG2</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -5704,9 +4303,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -5720,11 +4316,7 @@
           <t>DPG2</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -5733,11 +4325,6 @@
       <c r="E164" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5752,11 +4339,7 @@
           <t>DPG2</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -5766,9 +4349,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G165" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="166">
@@ -5782,11 +4362,7 @@
           <t>DPG2</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -5796,9 +4372,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G166" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -5812,11 +4385,7 @@
           <t>DPG2</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -5826,9 +4395,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G167" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="168">
@@ -5842,11 +4408,7 @@
           <t>DPG2</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -5855,11 +4417,6 @@
       <c r="E168" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5874,11 +4431,7 @@
           <t>DPG2</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -5887,11 +4440,6 @@
       <c r="E169" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5906,11 +4454,7 @@
           <t>DPG2a</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -5920,9 +4464,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G170" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -5936,11 +4477,7 @@
           <t>DPG2a</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -5949,11 +4486,6 @@
       <c r="E171" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -5968,11 +4500,7 @@
           <t>DPG2a</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -5982,9 +4510,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G172" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="173">
@@ -5998,11 +4523,7 @@
           <t>DPG2a</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -6012,9 +4533,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G173" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -6028,11 +4546,7 @@
           <t>DPG2a</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -6042,9 +4556,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G174" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="175">
@@ -6058,11 +4569,7 @@
           <t>DPG2a</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -6071,11 +4578,6 @@
       <c r="E175" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6090,11 +4592,7 @@
           <t>DPG2a</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -6103,11 +4601,6 @@
       <c r="E176" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6122,11 +4615,7 @@
           <t>DPG2b</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C177" t="inlineStr"/>
       <c r="D177" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -6136,9 +4625,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G177" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -6152,11 +4638,7 @@
           <t>DPG2b</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -6165,11 +4647,6 @@
       <c r="E178" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6184,11 +4661,7 @@
           <t>DPG2b</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -6198,9 +4671,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G179" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -6214,11 +4684,7 @@
           <t>DPG2b</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -6228,9 +4694,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G180" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -6244,11 +4707,7 @@
           <t>DPG2b</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -6258,9 +4717,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G181" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -6274,11 +4730,7 @@
           <t>DPG2b</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -6287,11 +4739,6 @@
       <c r="E182" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6306,11 +4753,7 @@
           <t>DPG2b</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -6319,11 +4762,6 @@
       <c r="E183" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6338,11 +4776,7 @@
           <t>DPG4</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -6351,11 +4785,6 @@
       <c r="E184" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6370,11 +4799,7 @@
           <t>DPG4</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -6383,11 +4808,6 @@
       <c r="E185" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6402,11 +4822,7 @@
           <t>DPG4</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -6415,11 +4831,6 @@
       <c r="E186" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6434,11 +4845,7 @@
           <t>DPG4</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -6447,11 +4854,6 @@
       <c r="E187" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6466,11 +4868,7 @@
           <t>DPG4</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -6480,9 +4878,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G188" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="189">
@@ -6496,11 +4891,7 @@
           <t>DPG4</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -6509,11 +4900,6 @@
       <c r="E189" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6528,11 +4914,7 @@
           <t>DPG4</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -6541,11 +4923,6 @@
       <c r="E190" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6560,11 +4937,7 @@
           <t>DPG5</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -6573,11 +4946,6 @@
       <c r="E191" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6592,11 +4960,7 @@
           <t>DPG5</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -6605,11 +4969,6 @@
       <c r="E192" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6624,11 +4983,7 @@
           <t>DPG5</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -6637,11 +4992,6 @@
       <c r="E193" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6656,11 +5006,7 @@
           <t>DPG5</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -6669,11 +5015,6 @@
       <c r="E194" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6688,11 +5029,7 @@
           <t>DPG5</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -6701,11 +5038,6 @@
       <c r="E195" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6720,11 +5052,7 @@
           <t>DPG5</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -6733,11 +5061,6 @@
       <c r="E196" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6752,11 +5075,7 @@
           <t>DPG5</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -6765,11 +5084,6 @@
       <c r="E197" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6784,11 +5098,7 @@
           <t>DPG5a</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -6797,11 +5107,6 @@
       <c r="E198" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6816,11 +5121,7 @@
           <t>DPG5a</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -6829,11 +5130,6 @@
       <c r="E199" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6848,11 +5144,7 @@
           <t>DPG5a</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -6861,11 +5153,6 @@
       <c r="E200" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6880,11 +5167,7 @@
           <t>DPG5a</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -6893,11 +5176,6 @@
       <c r="E201" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6912,11 +5190,7 @@
           <t>DPG5a</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -6925,11 +5199,6 @@
       <c r="E202" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6944,11 +5213,7 @@
           <t>DPG5a</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -6957,11 +5222,6 @@
       <c r="E203" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -6976,11 +5236,7 @@
           <t>DPG5a</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -6989,11 +5245,6 @@
       <c r="E204" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7008,11 +5259,7 @@
           <t>DPG5b</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -7021,11 +5268,6 @@
       <c r="E205" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7040,11 +5282,7 @@
           <t>DPG5b</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -7053,11 +5291,6 @@
       <c r="E206" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7072,11 +5305,7 @@
           <t>DPG5b</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -7085,11 +5314,6 @@
       <c r="E207" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7104,11 +5328,7 @@
           <t>DPG5b</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -7118,9 +5338,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -7134,11 +5351,7 @@
           <t>DPG5b</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -7147,11 +5360,6 @@
       <c r="E209" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7166,11 +5374,7 @@
           <t>DPG5b</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -7179,11 +5383,6 @@
       <c r="E210" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7198,11 +5397,7 @@
           <t>DPG5b</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -7211,11 +5406,6 @@
       <c r="E211" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7230,11 +5420,7 @@
           <t>DPG5c</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -7243,11 +5429,6 @@
       <c r="E212" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7262,11 +5443,7 @@
           <t>DPG5c</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -7275,11 +5452,6 @@
       <c r="E213" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7294,11 +5466,7 @@
           <t>DPG5c</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -7307,11 +5475,6 @@
       <c r="E214" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7326,11 +5489,7 @@
           <t>DPG5c</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -7339,11 +5498,6 @@
       <c r="E215" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7358,11 +5512,7 @@
           <t>DPG5c</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -7371,11 +5521,6 @@
       <c r="E216" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7390,11 +5535,7 @@
           <t>DPG5c</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -7403,11 +5544,6 @@
       <c r="E217" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7422,11 +5558,7 @@
           <t>DPG5c</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -7435,11 +5567,6 @@
       <c r="E218" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7454,11 +5581,7 @@
           <t>DPG5d</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -7467,11 +5590,6 @@
       <c r="E219" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7486,11 +5604,7 @@
           <t>DPG5d</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -7499,11 +5613,6 @@
       <c r="E220" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7518,11 +5627,7 @@
           <t>DPG5d</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -7531,11 +5636,6 @@
       <c r="E221" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7550,11 +5650,7 @@
           <t>DPG5d</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -7563,11 +5659,6 @@
       <c r="E222" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7582,11 +5673,7 @@
           <t>DPG5d</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -7595,11 +5682,6 @@
       <c r="E223" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7614,11 +5696,7 @@
           <t>DPG5d</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -7627,11 +5705,6 @@
       <c r="E224" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7646,11 +5719,7 @@
           <t>DPG5d</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -7659,11 +5728,6 @@
       <c r="E225" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7678,11 +5742,7 @@
           <t>DPG5f</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -7691,11 +5751,6 @@
       <c r="E226" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7710,11 +5765,7 @@
           <t>DPG5f</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -7723,11 +5774,6 @@
       <c r="E227" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7742,11 +5788,7 @@
           <t>DPG5f</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -7755,11 +5797,6 @@
       <c r="E228" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7774,11 +5811,7 @@
           <t>DPG5f</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -7787,11 +5820,6 @@
       <c r="E229" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7806,11 +5834,7 @@
           <t>DPG5f</t>
         </is>
       </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -7820,9 +5844,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G230" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -7836,11 +5857,7 @@
           <t>DPG5f</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -7849,11 +5866,6 @@
       <c r="E231" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7868,11 +5880,7 @@
           <t>DPG5f</t>
         </is>
       </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -7881,11 +5889,6 @@
       <c r="E232" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7900,11 +5903,7 @@
           <t>DPG5g</t>
         </is>
       </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -7913,11 +5912,6 @@
       <c r="E233" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7932,11 +5926,7 @@
           <t>DPG5g</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -7945,11 +5935,6 @@
       <c r="E234" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7964,11 +5949,7 @@
           <t>DPG5g</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -7977,11 +5958,6 @@
       <c r="E235" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -7996,11 +5972,7 @@
           <t>DPG5g</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -8009,11 +5981,6 @@
       <c r="E236" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8028,11 +5995,7 @@
           <t>DPG5g</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -8041,11 +6004,6 @@
       <c r="E237" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8060,11 +6018,7 @@
           <t>DPG5g</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -8073,11 +6027,6 @@
       <c r="E238" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8092,11 +6041,7 @@
           <t>DPG5g</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -8105,11 +6050,6 @@
       <c r="E239" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8124,11 +6064,7 @@
           <t>DPG5h</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -8137,11 +6073,6 @@
       <c r="E240" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8156,11 +6087,7 @@
           <t>DPG5h</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -8169,11 +6096,6 @@
       <c r="E241" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8188,11 +6110,7 @@
           <t>DPG5h</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -8201,11 +6119,6 @@
       <c r="E242" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8220,11 +6133,7 @@
           <t>DPG5h</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -8233,11 +6142,6 @@
       <c r="E243" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8252,11 +6156,7 @@
           <t>DPG5h</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -8266,9 +6166,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G244" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -8282,11 +6179,7 @@
           <t>DPG5h</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -8295,11 +6188,6 @@
       <c r="E245" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8314,11 +6202,7 @@
           <t>DPG5h</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -8327,11 +6211,6 @@
       <c r="E246" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8346,11 +6225,7 @@
           <t>DPG5i</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -8359,11 +6234,6 @@
       <c r="E247" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8378,11 +6248,7 @@
           <t>DPG5i</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -8391,11 +6257,6 @@
       <c r="E248" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8410,11 +6271,7 @@
           <t>DPG5i</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -8423,11 +6280,6 @@
       <c r="E249" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8442,11 +6294,7 @@
           <t>DPG5i</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -8455,11 +6303,6 @@
       <c r="E250" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8474,11 +6317,7 @@
           <t>DPG5i</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -8487,11 +6326,6 @@
       <c r="E251" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8506,11 +6340,7 @@
           <t>DPG5i</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -8519,11 +6349,6 @@
       <c r="E252" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8538,11 +6363,7 @@
           <t>DPG5i</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -8551,11 +6372,6 @@
       <c r="E253" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8570,11 +6386,7 @@
           <t>DPG5j</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -8583,11 +6395,6 @@
       <c r="E254" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8602,11 +6409,7 @@
           <t>DPG5j</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -8615,11 +6418,6 @@
       <c r="E255" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8634,11 +6432,7 @@
           <t>DPG5j</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -8647,11 +6441,6 @@
       <c r="E256" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8666,11 +6455,7 @@
           <t>DPG5j</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -8679,11 +6464,6 @@
       <c r="E257" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8698,11 +6478,7 @@
           <t>DPG5j</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -8711,11 +6487,6 @@
       <c r="E258" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8730,11 +6501,7 @@
           <t>DPG5j</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -8743,11 +6510,6 @@
       <c r="E259" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8762,11 +6524,7 @@
           <t>DPG5j</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -8775,11 +6533,6 @@
       <c r="E260" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8794,11 +6547,7 @@
           <t>DPG5k</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -8807,11 +6556,6 @@
       <c r="E261" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8826,11 +6570,7 @@
           <t>DPG5k</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -8839,11 +6579,6 @@
       <c r="E262" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8858,11 +6593,7 @@
           <t>DPG5k</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -8871,11 +6602,6 @@
       <c r="E263" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8890,11 +6616,7 @@
           <t>DPG5k</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -8903,11 +6625,6 @@
       <c r="E264" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8922,11 +6639,7 @@
           <t>DPG5k</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -8935,11 +6648,6 @@
       <c r="E265" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8954,11 +6662,7 @@
           <t>DPG5k</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -8967,11 +6671,6 @@
       <c r="E266" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -8986,11 +6685,7 @@
           <t>DPG5k</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -8999,11 +6694,6 @@
       <c r="E267" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9018,11 +6708,7 @@
           <t>DPG6</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -9031,11 +6717,6 @@
       <c r="E268" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9050,11 +6731,7 @@
           <t>DPG6</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -9063,11 +6740,6 @@
       <c r="E269" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9082,11 +6754,7 @@
           <t>DPG6</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -9095,11 +6763,6 @@
       <c r="E270" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9114,11 +6777,7 @@
           <t>DPG6</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -9127,11 +6786,6 @@
       <c r="E271" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9146,11 +6800,7 @@
           <t>DPG6</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -9159,11 +6809,6 @@
       <c r="E272" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9178,11 +6823,7 @@
           <t>DPG6</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -9191,11 +6832,6 @@
       <c r="E273" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9210,11 +6846,7 @@
           <t>DPG6</t>
         </is>
       </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -9223,11 +6855,6 @@
       <c r="E274" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9242,11 +6869,7 @@
           <t>DPG6a</t>
         </is>
       </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -9256,9 +6879,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G275" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="276">
@@ -9272,11 +6892,7 @@
           <t>DPG6a</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -9285,11 +6901,6 @@
       <c r="E276" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9304,11 +6915,7 @@
           <t>DPG6a</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -9318,9 +6925,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G277" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="278">
@@ -9334,11 +6938,7 @@
           <t>DPG6a</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -9347,11 +6947,6 @@
       <c r="E278" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9366,11 +6961,7 @@
           <t>DPG6a</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -9379,11 +6970,6 @@
       <c r="E279" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9398,11 +6984,7 @@
           <t>DPG6a</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -9411,11 +6993,6 @@
       <c r="E280" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9430,11 +7007,7 @@
           <t>DPG6a</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -9443,11 +7016,6 @@
       <c r="E281" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9462,11 +7030,7 @@
           <t>DPG6b</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -9475,11 +7039,6 @@
       <c r="E282" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9494,11 +7053,7 @@
           <t>DPG6b</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -9507,11 +7062,6 @@
       <c r="E283" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9526,11 +7076,7 @@
           <t>DPG6b</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -9539,11 +7085,6 @@
       <c r="E284" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9558,11 +7099,7 @@
           <t>DPG6b</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -9571,11 +7108,6 @@
       <c r="E285" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9590,11 +7122,7 @@
           <t>DPG6b</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -9603,11 +7131,6 @@
       <c r="E286" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9622,11 +7145,7 @@
           <t>DPG6b</t>
         </is>
       </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -9635,11 +7154,6 @@
       <c r="E287" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9654,11 +7168,7 @@
           <t>DPG6b</t>
         </is>
       </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -9667,11 +7177,6 @@
       <c r="E288" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9686,11 +7191,7 @@
           <t>DPG7</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -9700,9 +7201,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G289" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="290">
@@ -9716,11 +7214,7 @@
           <t>DPG7</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -9729,11 +7223,6 @@
       <c r="E290" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9748,11 +7237,7 @@
           <t>DPG7</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -9761,11 +7246,6 @@
       <c r="E291" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -9780,11 +7260,7 @@
           <t>DPG7</t>
         </is>
       </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -9794,9 +7270,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G292" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="293">
@@ -9810,11 +7283,7 @@
           <t>DPG7</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -9823,11 +7292,6 @@
       <c r="E293" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -9842,11 +7306,7 @@
           <t>DPG7</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -9855,11 +7315,6 @@
       <c r="E294" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -9874,11 +7329,7 @@
           <t>DPG7</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -9887,11 +7338,6 @@
       <c r="E295" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -9906,11 +7352,7 @@
           <t>DPG7a</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -9920,9 +7362,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G296" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -9936,11 +7375,7 @@
           <t>DPG7a</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -9950,9 +7385,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G297" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="298">
@@ -9966,11 +7398,7 @@
           <t>DPG7a</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -9979,11 +7407,6 @@
       <c r="E298" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -9998,11 +7421,7 @@
           <t>DPG7a</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -10012,9 +7431,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G299" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="300">
@@ -10028,11 +7444,7 @@
           <t>DPG7a</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -10041,11 +7453,6 @@
       <c r="E300" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10060,11 +7467,7 @@
           <t>DPG7a</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -10073,11 +7476,6 @@
       <c r="E301" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10092,11 +7490,7 @@
           <t>DPG7a</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -10105,11 +7499,6 @@
       <c r="E302" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10124,11 +7513,7 @@
           <t>DPG7b</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -10138,9 +7523,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G303" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="304">
@@ -10154,11 +7536,7 @@
           <t>DPG7b</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -10167,11 +7545,6 @@
       <c r="E304" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10186,11 +7559,7 @@
           <t>DPG7b</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -10199,11 +7568,6 @@
       <c r="E305" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10218,11 +7582,7 @@
           <t>DPG7b</t>
         </is>
       </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -10232,9 +7592,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G306" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="307">
@@ -10248,11 +7605,7 @@
           <t>DPG7b</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -10261,11 +7614,6 @@
       <c r="E307" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10280,11 +7628,7 @@
           <t>DPG7b</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -10293,11 +7637,6 @@
       <c r="E308" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10312,11 +7651,7 @@
           <t>DPG7b</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -10325,11 +7660,6 @@
       <c r="E309" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10344,11 +7674,7 @@
           <t>SC1</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -10357,11 +7683,6 @@
       <c r="E310" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10376,11 +7697,7 @@
           <t>SC1</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -10389,11 +7706,6 @@
       <c r="E311" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10408,11 +7720,7 @@
           <t>SC1</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -10421,11 +7729,6 @@
       <c r="E312" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10440,11 +7743,7 @@
           <t>SC1</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -10453,11 +7752,6 @@
       <c r="E313" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10472,11 +7766,7 @@
           <t>SC1</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -10485,11 +7775,6 @@
       <c r="E314" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10504,11 +7789,7 @@
           <t>SC1</t>
         </is>
       </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -10517,11 +7798,6 @@
       <c r="E315" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10536,11 +7812,7 @@
           <t>SC1</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -10549,11 +7821,6 @@
       <c r="E316" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10568,11 +7835,7 @@
           <t>SC2</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -10581,11 +7844,6 @@
       <c r="E317" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10600,11 +7858,7 @@
           <t>SC2</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -10613,11 +7867,6 @@
       <c r="E318" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10632,11 +7881,7 @@
           <t>SC2</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -10645,11 +7890,6 @@
       <c r="E319" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10664,11 +7904,7 @@
           <t>SC2</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -10677,11 +7913,6 @@
       <c r="E320" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10696,11 +7927,7 @@
           <t>SC2</t>
         </is>
       </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -10709,11 +7936,6 @@
       <c r="E321" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10728,11 +7950,7 @@
           <t>SC2</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -10741,11 +7959,6 @@
       <c r="E322" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>NA</t>
         </is>
       </c>
     </row>
@@ -10760,11 +7973,7 @@
           <t>SC2</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -10773,11 +7982,6 @@
       <c r="E323" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10792,11 +7996,7 @@
           <t>SC3</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -10805,11 +8005,6 @@
       <c r="E324" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10824,11 +8019,7 @@
           <t>SC3</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -10837,11 +8028,6 @@
       <c r="E325" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10856,11 +8042,7 @@
           <t>SC3</t>
         </is>
       </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -10869,11 +8051,6 @@
       <c r="E326" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10888,11 +8065,7 @@
           <t>SC3</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -10901,11 +8074,6 @@
       <c r="E327" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10920,11 +8088,7 @@
           <t>SC3</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -10933,11 +8097,6 @@
       <c r="E328" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10952,11 +8111,7 @@
           <t>SC3</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -10965,11 +8120,6 @@
       <c r="E329" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -10984,11 +8134,7 @@
           <t>SC3</t>
         </is>
       </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -10997,11 +8143,6 @@
       <c r="E330" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11016,11 +8157,7 @@
           <t>SC4</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -11029,11 +8166,6 @@
       <c r="E331" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11048,11 +8180,7 @@
           <t>SC4</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -11061,11 +8189,6 @@
       <c r="E332" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11080,11 +8203,7 @@
           <t>SC4</t>
         </is>
       </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -11093,11 +8212,6 @@
       <c r="E333" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11112,11 +8226,7 @@
           <t>SC4</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -11125,11 +8235,6 @@
       <c r="E334" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11144,11 +8249,7 @@
           <t>SC4</t>
         </is>
       </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -11157,11 +8258,6 @@
       <c r="E335" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11176,11 +8272,7 @@
           <t>SC4</t>
         </is>
       </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -11189,11 +8281,6 @@
       <c r="E336" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11208,11 +8295,7 @@
           <t>SC4</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -11221,11 +8304,6 @@
       <c r="E337" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11240,11 +8318,7 @@
           <t>SC4a</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -11254,9 +8328,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G338" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -11270,11 +8341,7 @@
           <t>SC4a</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -11284,9 +8351,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G339" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -11300,11 +8364,7 @@
           <t>SC4a</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -11314,9 +8374,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G340" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -11330,11 +8387,7 @@
           <t>SC4a</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -11344,9 +8397,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G341" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -11360,11 +8410,7 @@
           <t>SC4a</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -11374,9 +8420,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G342" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -11390,11 +8433,7 @@
           <t>SC4a</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -11403,11 +8442,6 @@
       <c r="E343" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11422,11 +8456,7 @@
           <t>SC4a</t>
         </is>
       </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -11435,11 +8465,6 @@
       <c r="E344" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11454,11 +8479,7 @@
           <t>SC4b</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -11467,11 +8488,6 @@
       <c r="E345" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11486,11 +8502,7 @@
           <t>SC4b</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -11499,11 +8511,6 @@
       <c r="E346" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11518,11 +8525,7 @@
           <t>SC4b</t>
         </is>
       </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C347" t="inlineStr"/>
       <c r="D347" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -11531,11 +8534,6 @@
       <c r="E347" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11550,11 +8548,7 @@
           <t>SC4b</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -11563,11 +8557,6 @@
       <c r="E348" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11582,11 +8571,7 @@
           <t>SC4b</t>
         </is>
       </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C349" t="inlineStr"/>
       <c r="D349" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -11595,11 +8580,6 @@
       <c r="E349" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11614,11 +8594,7 @@
           <t>SC4b</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C350" t="inlineStr"/>
       <c r="D350" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -11627,11 +8603,6 @@
       <c r="E350" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11646,11 +8617,7 @@
           <t>SC4b</t>
         </is>
       </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -11659,11 +8626,6 @@
       <c r="E351" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11678,11 +8640,7 @@
           <t>SC5</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -11692,9 +8650,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G352" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -11708,11 +8663,7 @@
           <t>SC5</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -11721,11 +8672,6 @@
       <c r="E353" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11740,11 +8686,7 @@
           <t>SC5</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -11754,9 +8696,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G354" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -11770,11 +8709,7 @@
           <t>SC5</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -11784,9 +8719,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G355" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -11800,11 +8732,7 @@
           <t>SC5</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -11813,11 +8741,6 @@
       <c r="E356" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11832,11 +8755,7 @@
           <t>SC5</t>
         </is>
       </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -11845,11 +8764,6 @@
       <c r="E357" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11864,11 +8778,7 @@
           <t>SC5</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C358" t="inlineStr"/>
       <c r="D358" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -11877,11 +8787,6 @@
       <c r="E358" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11896,11 +8801,7 @@
           <t>SC6</t>
         </is>
       </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -11909,11 +8810,6 @@
       <c r="E359" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11928,11 +8824,7 @@
           <t>SC6</t>
         </is>
       </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -11941,11 +8833,6 @@
       <c r="E360" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11960,11 +8847,7 @@
           <t>SC6</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -11973,11 +8856,6 @@
       <c r="E361" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -11992,11 +8870,7 @@
           <t>SC6</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -12005,11 +8879,6 @@
       <c r="E362" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12024,11 +8893,7 @@
           <t>SC6</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -12037,11 +8902,6 @@
       <c r="E363" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12056,11 +8916,7 @@
           <t>SC6</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -12069,11 +8925,6 @@
       <c r="E364" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12088,11 +8939,7 @@
           <t>SC6</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -12101,11 +8948,6 @@
       <c r="E365" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12120,11 +8962,7 @@
           <t>SC7</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -12133,11 +8971,6 @@
       <c r="E366" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12152,11 +8985,7 @@
           <t>SC7</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -12165,11 +8994,6 @@
       <c r="E367" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12184,11 +9008,7 @@
           <t>SC7</t>
         </is>
       </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -12197,11 +9017,6 @@
       <c r="E368" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12216,11 +9031,7 @@
           <t>SC7</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -12229,11 +9040,6 @@
       <c r="E369" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12248,11 +9054,7 @@
           <t>SC7</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -12261,11 +9063,6 @@
       <c r="E370" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12280,11 +9077,7 @@
           <t>SC7</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -12293,11 +9086,6 @@
       <c r="E371" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12312,11 +9100,7 @@
           <t>SC7</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
+      <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -12325,11 +9109,6 @@
       <c r="E372" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12344,11 +9123,7 @@
           <t>SC7a</t>
         </is>
       </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -12358,9 +9133,6 @@
         <is>
           <t>Bengaluru</t>
         </is>
-      </c>
-      <c r="G373" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="374">
@@ -12374,11 +9146,7 @@
           <t>SC7a</t>
         </is>
       </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -12387,11 +9155,6 @@
       <c r="E374" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12406,11 +9169,7 @@
           <t>SC7a</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -12419,11 +9178,6 @@
       <c r="E375" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12438,11 +9192,7 @@
           <t>SC7a</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -12451,11 +9201,6 @@
       <c r="E376" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G376" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12470,11 +9215,7 @@
           <t>SC7a</t>
         </is>
       </c>
-      <c r="C377" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -12483,11 +9224,6 @@
       <c r="E377" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12502,11 +9238,7 @@
           <t>SC7a</t>
         </is>
       </c>
-      <c r="C378" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -12515,11 +9247,6 @@
       <c r="E378" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G378" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12534,11 +9261,7 @@
           <t>SC7a</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -12547,11 +9270,6 @@
       <c r="E379" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G379" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12566,11 +9284,7 @@
           <t>SC7b</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
           <t>Bengaluru – BWSSB</t>
@@ -12579,11 +9293,6 @@
       <c r="E380" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12598,11 +9307,7 @@
           <t>SC7b</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
           <t>Bengaluru – BMTC</t>
@@ -12611,11 +9316,6 @@
       <c r="E381" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12630,11 +9330,7 @@
           <t>SC7b</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>Bengaluru – BDA</t>
@@ -12643,11 +9339,6 @@
       <c r="E382" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12662,11 +9353,7 @@
           <t>SC7b</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
           <t>Bengaluru – BMRCL</t>
@@ -12675,11 +9362,6 @@
       <c r="E383" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G383" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12694,11 +9376,7 @@
           <t>SC7b</t>
         </is>
       </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>Bengaluru – BMRDA</t>
@@ -12707,11 +9385,6 @@
       <c r="E384" t="inlineStr">
         <is>
           <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12726,11 +9399,7 @@
           <t>SC7b</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C385" t="inlineStr"/>
       <c r="D385" t="inlineStr">
         <is>
           <t>Surat – SUDA</t>
@@ -12739,11 +9408,6 @@
       <c r="E385" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G385" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>
@@ -12758,11 +9422,7 @@
           <t>SC7b</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr">
-        <is>
-          <t>SQ</t>
-        </is>
-      </c>
+      <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
           <t>Surat – GMRC</t>
@@ -12771,11 +9431,6 @@
       <c r="E386" t="inlineStr">
         <is>
           <t>Surat</t>
-        </is>
-      </c>
-      <c r="G386" t="inlineStr">
-        <is>
-          <t>?</t>
         </is>
       </c>
     </row>

--- a/scoring/2027/results/ASICS_2027_Scores.xlsx
+++ b/scoring/2027/results/ASICS_2027_Scores.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4574,7 +4574,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
     </row>

--- a/scoring/2027/results/ASICS_2027_Scores.xlsx
+++ b/scoring/2027/results/ASICS_2027_Scores.xlsx
@@ -481,17 +481,17 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.85</v>
+        <v>1.08</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="D2">
         <f>IFERROR(ROUND(AVERAGE(B2,C2),2),"")</f>
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -500,22 +500,18 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="B3" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.77</v>
       </c>
       <c r="D3">
         <f>IFERROR(ROUND(AVERAGE(B3,C3),2),"")</f>
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -687,8 +683,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>10</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -717,10 +715,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G5" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -813,8 +809,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>3.33</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -875,8 +873,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>3.33</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -905,10 +905,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G11" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="12">
@@ -1031,10 +1029,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1159,10 +1155,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G19" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="20">
@@ -1191,8 +1185,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1573,8 +1569,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>10</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1635,8 +1633,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>10</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1921,10 +1921,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -2145,8 +2143,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>1.67</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -2207,8 +2207,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>1.67</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -2269,8 +2271,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>1.67</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -2331,8 +2335,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>1.67</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -2617,10 +2623,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G65" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="66">
@@ -3061,10 +3065,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G79" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="80">
@@ -3185,10 +3187,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G83" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -4611,10 +4611,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G129" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="130">
@@ -5169,10 +5167,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -5553,10 +5549,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G159" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="160">
@@ -6065,10 +6059,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G175" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="176">
@@ -6253,10 +6245,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G181" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="182">
@@ -6315,10 +6305,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G183" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -6377,10 +6365,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G185" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="186">
@@ -6439,10 +6425,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G187" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="188">
@@ -6821,10 +6805,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G199" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="200">
@@ -7045,8 +7027,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G206" t="n">
-        <v>5</v>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -7075,10 +7059,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G207" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="208">
@@ -9709,8 +9691,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G290" t="n">
-        <v>3.75</v>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -9931,8 +9915,10 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G297" t="n">
-        <v>2.5</v>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -10344,7 +10330,7 @@
         </is>
       </c>
       <c r="G310" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="311">
@@ -10788,7 +10774,7 @@
         </is>
       </c>
       <c r="G324" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325">
@@ -12975,10 +12961,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G394" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="395">
@@ -13163,10 +13147,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G400" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="401">
@@ -13833,10 +13815,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G421" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="422">
@@ -14727,10 +14707,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G449" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="450">
@@ -15397,10 +15375,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G470" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G470" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="471">
@@ -15621,10 +15597,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G477" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="478">
@@ -16947,10 +16921,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G519" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="520">

--- a/scoring/2027/results/ASICS_2027_Scores.xlsx
+++ b/scoring/2027/results/ASICS_2027_Scores.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1.14</v>
@@ -491,7 +491,7 @@
         <v/>
       </c>
       <c r="E2" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.77</v>
+        <v>1.49</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>0.77</v>
@@ -511,7 +511,7 @@
         <v/>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -683,10 +683,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G4" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -809,10 +807,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G8" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="9">
@@ -873,10 +869,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G10" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="11">
@@ -1951,10 +1945,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G44" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="45">
@@ -2207,10 +2199,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G52" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="53">
@@ -2271,10 +2261,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G54" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="55">
@@ -2335,10 +2323,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G56" t="n">
+        <v>1.67</v>
       </c>
     </row>
     <row r="57">
@@ -2749,10 +2735,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G69" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="70">
@@ -4487,10 +4471,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G125" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="126">
@@ -4549,10 +4531,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G127" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="128">
@@ -4671,10 +4651,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G131" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="132">
@@ -5105,10 +5083,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G145" t="n">
+        <v>3.33</v>
       </c>
     </row>
     <row r="146">
@@ -6027,10 +6003,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G174" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="175">
@@ -6089,10 +6063,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G176" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="177">
@@ -6183,10 +6155,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G179" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="180">
@@ -6485,10 +6455,8 @@
           <t>Surat</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G189" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -7027,10 +6995,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G206" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="207">
@@ -7153,10 +7119,8 @@
           <t>Bengaluru</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
+      <c r="G210" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="211">
